--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96844903</v>
+        <v>96844884</v>
       </c>
       <c r="B2" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6003295</v>
+        <v>426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720531.703412971</v>
+        <v>720440</v>
       </c>
       <c r="R2" t="n">
-        <v>6418223.539932557</v>
+        <v>6418164</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2021-09-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96844890</v>
+        <v>96844934</v>
       </c>
       <c r="B3" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>3674</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720466.5712820985</v>
+        <v>720538</v>
       </c>
       <c r="R3" t="n">
-        <v>6418183.694278332</v>
+        <v>6418214</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2021-09-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96844869</v>
+        <v>96844868</v>
       </c>
       <c r="B4" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720537.4792937298</v>
+        <v>720522</v>
       </c>
       <c r="R4" t="n">
-        <v>6418186.526993497</v>
+        <v>6418158</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2021-09-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96844934</v>
+        <v>96844869</v>
       </c>
       <c r="B5" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720538.1187102407</v>
+        <v>720537</v>
       </c>
       <c r="R5" t="n">
-        <v>6418213.76021311</v>
+        <v>6418187</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2021-09-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96844901</v>
+        <v>96844870</v>
       </c>
       <c r="B6" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720516.0021063711</v>
+        <v>720458</v>
       </c>
       <c r="R6" t="n">
-        <v>6418198.144907601</v>
+        <v>6418263</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2021-09-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,6 +1157,500 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96844890</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>720466</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6418184</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96844882</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93194</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>239737</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knölig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum cumulatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>K.A.Harrison</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>720458</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6418165</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>95824182</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75312</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6000146</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Coniocarpon fallax</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Grube</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Olarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>720508</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6418163</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Olarve 14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Död ask</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>96844901</v>
+      </c>
+      <c r="B10" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>720516</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6418198</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>96844903</v>
+      </c>
+      <c r="B11" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>720532</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6418223</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844884</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844934</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844868</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844869</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844870</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844890</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844882</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95824182</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844901</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,8 +1701,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844903</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>